--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Eventi e manifestazioni.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Eventi e manifestazioni.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="122">
   <si>
     <r>
       <t xml:space="preserve">
@@ -173,7 +173,7 @@
     <t>Utilizza il testo indicato per il pulsante. Inserisci il link alla pagina web che rimanda al servizio.</t>
   </si>
   <si>
-    <t>Vedi tutti gli eventi</t>
+    <t>Trova eventi</t>
   </si>
   <si>
     <t>Link a termini e condizioni d'uso</t>
@@ -1248,7 +1248,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -1337,12 +1337,6 @@
       </rPr>
       <t>Note aggiuntive</t>
     </r>
-  </si>
-  <si>
-    <t>✨Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi dell'evento tramite notifica push.</t>
-  </si>
-  <si>
-    <t>✨Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi dell'appuntamento tramite notifica push.</t>
   </si>
 </sst>
 </file>
@@ -2329,13 +2323,13 @@
         <v>61</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>122</v>
+        <v>61</v>
       </c>
       <c r="D11" s="34" t="s">
         <v>61</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>123</v>
+        <v>61</v>
       </c>
       <c r="F11" s="34" t="s">
         <v>61</v>
